--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N15_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N15_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>12.74754878398196</v>
+        <v>2.071476677397069</v>
       </c>
       <c r="D2" t="n">
-        <v>11.45751274140455</v>
+        <v>1.86184582047824</v>
       </c>
       <c r="E2" t="n">
-        <v>12.69266684052853</v>
+        <v>2.062558361585886</v>
       </c>
       <c r="F2" t="n">
-        <v>12.83126274762706</v>
+        <v>2.085080196489397</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>46.19508418002082</v>
+        <v>7.506701179253383</v>
       </c>
       <c r="D3" t="n">
-        <v>8.395913924184967</v>
+        <v>1.364336012680057</v>
       </c>
       <c r="E3" t="n">
-        <v>12.69266684052853</v>
+        <v>2.062558361585886</v>
       </c>
       <c r="F3" t="n">
-        <v>12.83126274762706</v>
+        <v>2.085080196489397</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.29504180056385</v>
+        <v>3.622944292591626</v>
       </c>
       <c r="D4" t="n">
-        <v>15.40930235129171</v>
+        <v>2.504011632084903</v>
       </c>
       <c r="E4" t="n">
-        <v>12.69266684052853</v>
+        <v>2.062558361585886</v>
       </c>
       <c r="F4" t="n">
-        <v>12.83126274762706</v>
+        <v>2.085080196489397</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>30.84300749134414</v>
+        <v>5.011988717343423</v>
       </c>
       <c r="D5" t="n">
-        <v>27.73594880770199</v>
+        <v>4.507091681251574</v>
       </c>
       <c r="E5" t="n">
-        <v>12.69266684052853</v>
+        <v>2.062558361585886</v>
       </c>
       <c r="F5" t="n">
-        <v>12.83126274762706</v>
+        <v>2.085080196489397</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>43.87864578078449</v>
+        <v>7.13027993937748</v>
       </c>
       <c r="D6" t="n">
-        <v>43.29325869089011</v>
+        <v>7.035154537269642</v>
       </c>
       <c r="E6" t="n">
-        <v>12.69266684052853</v>
+        <v>2.062558361585886</v>
       </c>
       <c r="F6" t="n">
-        <v>12.83126274762706</v>
+        <v>2.085080196489397</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
